--- a/editing/CAD_Explorer_text.xlsx
+++ b/editing/CAD_Explorer_text.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1008,33 +1008,37 @@
       <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Dataset header (title, tagline, stats)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>H011</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Top bar and navigation</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Dataset header (title, tagline, stats)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>&lt;span class="hint" style="align-self:center"&gt;Choose a dataset:&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1056,15 +1060,11 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>&lt;span class="hint" style="align-self:center"&gt;Choose a dataset:&lt;/span&gt;</t>
+          <t>genes you can look up</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;div&gt;</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>The experiment in 60 seconds</t>
+          <t>up</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -1108,66 +1108,66 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>genes you can look up</t>
+          <t>down</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>H015</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Dataset header (title, tagline, stats)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>up</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Explore a gene</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>H016</t>
+          <t>H015</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Dataset header (title, tagline, stats)</t>
+          <t>Explore a gene</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>&lt;div&gt;</t>
+          <t>&lt;h2&gt;</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>down</t>
+          <t>Explore a gene</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>H016</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Explore a gene</t>
         </is>
       </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>&lt;input&gt; placeholder</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Type a gene name… e.g. Cdk1</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1182,16 +1182,20 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;</t>
+          <t>&lt;div&gt;</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Explore a gene</t>
+          <t>&lt;span class="hint" style="align-self:center"&gt;Try:&lt;/span&gt;</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1206,12 +1210,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>&lt;input&gt; placeholder</t>
+          <t>&lt;button&gt;</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Type a gene name… e.g. Cdk1</t>
+          <t>🎲 Show me a random interesting gene</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
@@ -1235,7 +1239,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>&lt;span class="hint" style="align-self:center"&gt;Try:&lt;/span&gt;</t>
+          <t>&lt;span class="name" id="g-name"&gt;-&lt;/span&gt;&lt;span id="g-badges"&gt;&lt;/span&gt;</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
@@ -1258,12 +1262,12 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>🎲 Show me a random interesting gene</t>
+          <t>Expression in each dish</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr"/>
@@ -1282,20 +1286,16 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>&lt;div&gt;</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>&lt;span class="name" id="g-name"&gt;-&lt;/span&gt;&lt;span id="g-badges"&gt;&lt;/span&gt;</t>
+          <t>log scale</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Expression in each dish</t>
+          <t>Bars = average · dots = each individual dish (replicate)</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>log scale</t>
+          <t>What this means</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
@@ -1358,16 +1358,20 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>&lt;p&gt;</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Bars = average · dots = each individual dish (replicate)</t>
+          <t>Share this gene: &lt;span class="mono" id="g-link"&gt;&lt;/span&gt;</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="7" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1382,64 +1386,43 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;div&gt;</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>What this means</t>
+          <t>Search for a gene.</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>H026</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Explore a gene</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Share this gene: &lt;span class="mono" id="g-link"&gt;&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Big picture plot</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>H027</t>
+          <t>H026</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Explore a gene</t>
+          <t>Big picture plot</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>&lt;div&gt;</t>
+          <t>&lt;h2&gt;</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Search for a gene above, click a chip, or pick a random one to get started.</t>
+          <t>Big picture</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr"/>
@@ -1448,19 +1431,19 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Big picture plot</t>
+          <t>Compare plot</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>H028</t>
+          <t>H027</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Big picture plot</t>
+          <t>Compare plot</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -1470,7 +1453,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Big picture</t>
+          <t>Compare</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr"/>
@@ -1479,19 +1462,19 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Compare plot</t>
+          <t>Explore by theme</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>H029</t>
+          <t>H028</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Compare plot</t>
+          <t>Explore by theme</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -1501,62 +1484,62 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>Explore by theme</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>H029</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Explore by theme</t>
         </is>
       </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Average CPM</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>H030</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Explore by theme</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Explore by theme</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr"/>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Pathways</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>H031</t>
+          <t>H030</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Explore by theme</t>
+          <t>Pathways</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;h2&gt;</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Genes rarely act alone. Pick a group to see how a whole biological program responded.</t>
+          <t>Pathways: what kind of biology changed?</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr"/>
@@ -1565,105 +1548,101 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>H032</t>
+          <t>H031</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Explore by theme</t>
+          <t>Pathways</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;button&gt;</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Values are average CPM. Click a row to open that gene.</t>
+          <t>↑ Up in differentiated</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>H032</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Pathways</t>
         </is>
       </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>&lt;button&gt;</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>↓ Down in differentiated</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>H033</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Pathways</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Pathways: what kind of biology changed?</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Your own data (upload)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>H034</t>
+          <t>H033</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Pathways</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;h2&gt;</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Individual genes are hard to interpret. Instead we ask: of the genes that changed, are any &lt;em&gt;known biological programs&lt;/em&gt; over-represented? Each bar is a pathway or Gene Ontology term; longer and further left means more surprising. &lt;strong style="color:var(--gold)"&gt;Click a term&lt;/strong&gt; to see which genes put it there, then click a gene to open it.</t>
+          <t>Analyze your own data</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>H035</t>
+          <t>H034</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Pathways</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>↑ Up in differentiated</t>
+          <t>1 · Choose a file</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr"/>
@@ -1672,22 +1651,22 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>H036</t>
+          <t>H035</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Pathways</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>&lt;p&gt;</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>↓ Down in differentiated</t>
+          <t>Tab- or comma-separated. First column = gene name, other columns = samples.</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr"/>
@@ -1696,74 +1675,74 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>H037</t>
+          <t>H036</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Pathways</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;p&gt;</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Protein interaction network (STRING)</t>
+          <t>Examples: &lt;a href="example_undiff_vs_diff.csv" download style="color:var(--gold)"&gt;real (1v1)&lt;/a&gt; · &lt;a href="example_practice_SIMULATED.csv" download style="color:var(--gold)"&gt;simulated (3v3)&lt;/a&gt;</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
-      <c r="F47" s="7" t="inlineStr"/>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>H038</t>
+          <t>H037</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Pathways</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Genes do not work alone. This map connects the strongest-changing proteins that are &lt;em&gt;known to physically interact or act together&lt;/em&gt;, from the STRING database. Tight clusters are working machines. &lt;strong style="color:var(--gold)"&gt;Drag nodes, scroll to zoom, click one&lt;/strong&gt; to open that gene.</t>
+          <t>2 · Assign each sample to a group</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr"/>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>H039</t>
+          <t>H038</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Pathways</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>&lt;div&gt;</t>
+          <t>&lt;p&gt;</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>&lt;span&gt;&lt;i style="background:#e05252"&gt;&lt;/i&gt;higher in differentiated&lt;/span&gt;&lt;span&gt;&lt;i style="background:#4a90d9"&gt;&lt;/i&gt;lower in differentiated&lt;/span&gt;&lt;span class="hint"&gt;bigger circle = more connections&lt;/span&gt;</t>
+          <t>Results read as &lt;strong style="color:var(--text)"&gt;B relative to A&lt;/strong&gt;. One group on its own is fine: you get expression levels, no comparison.</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
@@ -1774,11 +1753,28 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>H039</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Your own data (upload)</t>
         </is>
       </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Group A: the starting point</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -1793,12 +1789,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;</t>
+          <t>&lt;input&gt; value</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Analyze your own data</t>
+          <t>Undifferentiated</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr"/>
@@ -1817,20 +1813,16 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Have your own RNA-seq table? Load it here and explore it with the same tools. &lt;strong style="color:var(--text)"&gt;Everything runs inside your browser&lt;/strong&gt;. The file is never uploaded anywhere, and it disappears when you close the page.</t>
+          <t>Group B: what you compare against it</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr"/>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
@@ -1845,12 +1837,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;input&gt; value</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1 · Choose a file</t>
+          <t>Differentiated</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr"/>
@@ -1869,20 +1861,16 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Accepted: a tab- or comma-separated table with one row per gene. Either the standard &lt;span class="mono"&gt;expression-matrix.tsv&lt;/span&gt; from the sequencing provider (columns &lt;span class="mono"&gt;gene_name&lt;/span&gt;, &lt;span class="mono"&gt;gene_biotype&lt;/span&gt;, &lt;span class="mono"&gt;&amp;lt;sample&amp;gt;_cpm&lt;/span&gt;…), or a simple table whose first column is the gene name and every other column is a sample of raw counts or CPM.</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr"/>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
@@ -1897,22 +1885,16 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>No file handy? Try one of these:&lt;br&gt;
-        · &lt;a href="example_undiff_vs_diff.csv" download style="color:var(--gold)"&gt;example_undiff_vs_diff.csv&lt;/a&gt;: the &lt;strong&gt;real&lt;/strong&gt; undifferentiated/differentiated counts (1 dish each, so no statistics, which is the lesson).&lt;br&gt;
-        · &lt;a href="example_practice_SIMULATED.csv" download style="color:var(--gold)"&gt;example_practice_SIMULATED.csv&lt;/a&gt;: &lt;strong&gt;simulated&lt;/strong&gt; 3-vs-3 replicates built by adding random noise to those real values. Use it to see the statistics working; do &lt;em&gt;not&lt;/em&gt; draw biology from it.</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1927,12 +1909,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>2 · Assign each sample to a group</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr"/>
@@ -1951,20 +1933,16 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;</t>
+          <t>&lt;td&gt;</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Every comparison needs a starting point and something to compare against it. In this experiment the starting point is &lt;strong style="color:var(--text)"&gt;undifferentiated&lt;/strong&gt; cells (Group A: still dividing in serum), and they are compared against &lt;strong style="color:var(--text)"&gt;differentiated&lt;/strong&gt; cells (Group B: serum removed for 5 days). Everything is reported as &lt;strong style="color:var(--text)"&gt;B relative to A&lt;/strong&gt;, so a gene shown as "up" is higher in differentiated cells. Studying something else? Just rename the groups.</t>
+          <t>Load a file first.</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr"/>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -1984,7 +1962,7 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Group A: the starting point</t>
+          <t>values are already CPM (don't rescale)</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr"/>
@@ -2003,12 +1981,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>&lt;input&gt; value</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Undifferentiated</t>
+          <t>keep protein-coding genes only (if the file says)</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
@@ -2027,12 +2005,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>&lt;button&gt;</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Group B: what you compare against it</t>
+          <t>Run analysis →</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr"/>
@@ -2051,60 +2029,43 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>&lt;input&gt; value</t>
+          <t>&lt;button&gt;</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Differentiated</t>
+          <t>⬇ Export results (CSV)</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>H051</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Your own data (upload)</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Sample</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="7" t="inlineStr"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>H052</t>
+          <t>H051</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>&lt;th&gt;</t>
+          <t>&lt;h2&gt;</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Does your result match the published study?</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr"/>
@@ -2113,22 +2074,22 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>H053</t>
+          <t>H052</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>&lt;th&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Gene-by-gene agreement</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
@@ -2137,22 +2098,22 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>H054</t>
+          <t>H053</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>&lt;td&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Load a file first.</t>
+          <t>Landmark genes: the ones this experiment is known for</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
@@ -2161,22 +2122,22 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>H055</t>
+          <t>H054</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>values are already CPM (don't rescale)</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr"/>
@@ -2185,22 +2146,22 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>H056</t>
+          <t>H055</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>keep protein-coding genes only (if the file says)</t>
+          <t>What it is</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr"/>
@@ -2209,22 +2170,22 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>H057</t>
+          <t>H056</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Run analysis →</t>
+          <t>Your log₂FC</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
@@ -2233,22 +2194,22 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>H058</t>
+          <t>H057</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Your own data (upload)</t>
+          <t>Cross-check vs published</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>⬇ Export results (CSV)</t>
+          <t>Published log₂FC</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
@@ -2257,1047 +2218,63 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
+          <t>H058</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>&lt;th&gt;</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Agree?</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
           <t>H059</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Your own data (upload)</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>&lt;strong&gt;What happens when you click Run:&lt;/strong&gt; counts are rescaled to CPM (counts per million) so dishes are comparable; each gene's average in Group B (differentiated) is divided by its average in Group A (undifferentiated) to give a log₂ fold change. If &lt;em&gt;both&lt;/em&gt; groups have at least two dishes, a Welch t-test on log₂(CPM+1) gives a p-value per gene, corrected for testing thousands of genes at once (Benjamini–Hochberg). That's a simplified classroom version of what DESeq2 does: good for learning, not for publishing.
-    &lt;br&gt;&lt;br&gt;&lt;strong&gt;Expect fewer hits than a real tool.&lt;/strong&gt; With only 2–3 dishes per group a t-test can never produce a very small p-value (there is too little information), and after correcting for ~12,000 genes only the strongest changes survive. Real tools like DESeq2 get more power by sharing information across genes. If a gene looks obviously different but comes out "not significant", that is usually this limitation, not evidence the gene is unchanged.</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Cross-check vs published</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>H060</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Does your result match the published study?</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="7" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>H061</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Your uploaded data is compared, gene by gene, against &lt;strong style="color:var(--text)"&gt;Cevallos et al. 2025&lt;/strong&gt;, an independent published experiment on the same cells. Agreement between two separate labs is the strongest evidence a finding is real.</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>H062</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>&lt;h3&gt;</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>Gene-by-gene agreement</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr"/>
-      <c r="F74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>H063</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Each dot is a gene. &lt;strong style="color:var(--text)"&gt;Across&lt;/strong&gt; = how much it changed in &lt;em&gt;your&lt;/em&gt; data. &lt;strong style="color:var(--text)"&gt;Up&lt;/strong&gt; = how much it changed in the published study. If the two experiments agree, dots line up along the &lt;span style="color:var(--gold)"&gt;gold diagonal&lt;/span&gt;. Dots in the top-right and bottom-left quadrants agree in direction; the other two quadrants disagree. &lt;strong style="color:var(--gold)"&gt;Click a dot&lt;/strong&gt; to open that gene.</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr"/>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>H064</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>&lt;h3&gt;</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Landmark genes: the ones this experiment is known for</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="7" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>H065</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>These are the genes the published study reports most strongly. Does your data reproduce them?</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr"/>
-      <c r="F77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>H066</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="7" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>H067</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>What it is</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr"/>
-      <c r="F79" s="7" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>H068</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Your log₂FC</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="7" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>H069</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Published log₂FC</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>H070</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Agree?</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr"/>
-      <c r="F82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>H071</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
-        <is>
-          <t>&lt;h2&gt;</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr"/>
-      <c r="F84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>H072</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>RNA-seq: what is actually being measured?</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr"/>
-      <c r="F85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>H073</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>Every cell constantly copies its active genes into RNA. RNA-seq collects all of that RNA, reads it, and counts how many reads came from each gene. More reads = the gene is more "on". It's a snapshot of what the cell is doing, not what it &lt;em&gt;could&lt;/em&gt; do.</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr"/>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>H074</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>CPM: counts per million</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>H075</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Different dishes get different numbers of total reads (one might have 15 million, another 3 million). To compare fairly, each gene's count is scaled to "per million reads". &lt;strong&gt;CPM is the number on the y-axis of the gene chart.&lt;/strong&gt; Roughly: under 1 = basically off, 10–100 = solidly on, 1000+ = a heavy hitter.</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr"/>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>H076</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>Replicates: why the number of dots matters</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr"/>
-      <c r="F89" s="7" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>H077</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>A &lt;strong&gt;replicate&lt;/strong&gt; is an independent dish treated the same way. Replicates tell you how much a gene wobbles naturally. With several dishes per condition we can ask "is the difference bigger than the wobble?" That's a statistical test. With only one dish per condition there's no wobble to measure, so we can only &lt;em&gt;describe&lt;/em&gt; a difference, not &lt;em&gt;test&lt;/em&gt; it. The undifferentiated-vs-differentiated dataset is exactly that situation.</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr"/>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>H078</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>log₂ fold change: the "how much" number</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr"/>
-      <c r="F91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>H079</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Fold change is the ratio: treated ÷ control. We take log₂ so up and down are symmetric: &lt;strong&gt;+1 = doubled, +2 = 4×, +3 = 8×; −1 = halved, −3 = one-eighth.&lt;/strong&gt; A log₂FC of −3.5 means the gene dropped to about 1/11th of its starting level.</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr"/>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>H080</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>p-value and adjusted p-value: the "how sure" number</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr"/>
-      <c r="F93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>H081</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>A &lt;strong&gt;p-value&lt;/strong&gt; is the chance you'd see a difference this big by luck if nothing were really going on. Small = convincing. But we test ~13,000 genes at once, so some will look convincing by luck alone. The &lt;strong&gt;adjusted p-value&lt;/strong&gt; (also called FDR) corrects for that. We call a gene "significant" when adjusted p &amp;lt; 0.05 &lt;em&gt;and&lt;/em&gt; it changed at least 2× (|log₂FC| &amp;gt; 1).</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr"/>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>H082</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>DESeq2 vs the t-test used for your own data</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>H083</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>DESeq2 is the standard tool for asking "which genes really changed?" It models count noise carefully and borrows information across genes, which makes it reliable even with few replicates. The &lt;strong&gt;Welch t-test&lt;/strong&gt; this page runs on uploaded data is a simpler cousin: it compares the two groups' averages relative to their spread, gene by gene. It captures the idea, and it's what you'd learn in an intro stats course, but for a real paper you'd use DESeq2 or edgeR.</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr"/>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>H084</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Volcano plot: reading it in 10 seconds</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>H085</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Left–right is effect size, up is confidence. The shape looks like an erupting volcano because big changes tend to be confident changes. &lt;strong&gt;Look at the top-left and top-right&lt;/strong&gt;: those genes changed a lot &lt;em&gt;and&lt;/em&gt; we're sure about it. Dots near the bottom middle are noise. You only get a volcano when there are replicates to compute p-values from.</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr"/>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>H086</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>MA plot: the volcano's cousin for n=1</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr"/>
-      <c r="F99" s="7" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>H087</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>With one dish per condition there are no p-values, so instead we plot each gene's fold change (up–down) against how strongly it's expressed overall (left–right). Genes far up or down changed a lot. Trust the ones on the &lt;em&gt;right&lt;/em&gt; more: highly expressed genes are measured precisely, while a "10× change" in a gene with 2 reads is mostly noise.</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr"/>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>H088</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Batch effect: why samples from different runs need care</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr"/>
-      <c r="F101" s="7" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>H089</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Samples processed on different days, by different hands, or on different sequencing runs pick up small systematic differences that have nothing to do with biology. When two conditions were sequenced separately, some of their difference could be batch, not treatment. Big, biologically coherent changes are still informative; small ones aren't.</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr"/>
-      <c r="F102" s="7" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>H090</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Differentiation: what "undifferentiated vs differentiated" means</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr"/>
-      <c r="F103" s="7" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>H091</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>CAD cells can be kept dividing in a stem-like state, or nudged (by removing serum) to stop dividing and grow long neuron-like processes. That switch, from a proliferating cell to a mature, specialised neuron, is called differentiation, and it rewires thousands of genes: division genes go quiet, neuron-identity genes switch on.</t>
-        </is>
-      </c>
-      <c r="E104" s="8" t="inlineStr"/>
-      <c r="F104" s="7" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>H092</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>CAD cells: what are they?</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr"/>
-      <c r="F105" s="7" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>H093</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>CAD cells are a mouse line derived from &lt;strong&gt;Cath.a&lt;/strong&gt; cells, a central-nervous-system catecholaminergic line, the kind of neuron that makes dopamine and noradrenaline. In serum they divide; in serum-free media they stop dividing and grow neurite-like processes. That makes them a convenient, cheap model for asking what happens as a neuron matures, without needing animals.</t>
-        </is>
-      </c>
-      <c r="E106" s="8" t="inlineStr"/>
-      <c r="F106" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>H094</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Replication: why two datasets of the same experiment?</t>
-        </is>
-      </c>
-      <c r="E107" s="8" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="7" t="inlineStr">
-        <is>
-          <t>H095</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>The backup data is from this lab (1 dish per condition). The other built-in dataset is an independent, &lt;strong&gt;published&lt;/strong&gt; study (Cevallos et al. 2025) that did the same experiment with 3 dishes per condition and deposited the results publicly. Getting the same answer from different hands, different cells and different sequencing runs is the strongest evidence a finding is real, much stronger than any single p-value. Try looking up &lt;span class="mono"&gt;Id3&lt;/span&gt; in both.</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr"/>
-      <c r="F108" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>H096</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>&lt;summary&gt;</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Where published data lives: GEO</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr"/>
-      <c r="F109" s="7" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>H097</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>&lt;div&gt;</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>The &lt;strong&gt;Gene Expression Omnibus (GEO)&lt;/strong&gt; is a free public archive at NCBI where researchers must deposit sequencing data when they publish. Every dataset gets an accession like &lt;span class="mono"&gt;GSE291553&lt;/span&gt;. Anyone can download it, which is how the published dataset got here, and how you could analyse someone else\'s experiment yourself using the upload tool above.</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr"/>
-      <c r="F110" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>H098</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>Learn the terms (glossary)</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>&lt;footer&gt;</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>CAD Gene Explorer · mouse RNA-seq · built for teaching · your uploaded files never leave your computer</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr"/>
-      <c r="F111" s="7" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A42:F42"/>
+  <mergeCells count="10">
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3309,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3451,20 +2428,16 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>intro paragraph</t>
+          <t>group A name</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;An independent group ran the same experiment properly replicated: &lt;strong style="color:var(--text)"&gt;3 dishes per condition&lt;/strong&gt;, differentiated for 5 days in serum-free media, and deposited the results publicly.&lt;/p&gt;&lt;p&gt;Because there are replicates, this dataset has &lt;strong style="color:var(--gold)"&gt;real p-values&lt;/strong&gt;. Use it to check anything you found in the backup data. Start with &lt;strong style="color:var(--gold)"&gt;Id3&lt;/strong&gt;.&lt;/p&gt;&lt;p class="hint"&gt;Source: Cevallos CA, White AL, Fazio BA, Wendt LS, Feng JW, Posfai D, Horton AL, Warrick JM, Quintero-Carmona OA. &lt;em&gt;Transcriptomic Analysis of CAD Cell Differentiation.&lt;/em&gt; microPublication Biology, 2025. Data: &lt;a href="https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE291553" target="_blank" rel="noopener" style="color:var(--gold)"&gt;GEO GSE291553&lt;/a&gt;. The authors published a summary table, so the two bars are &lt;strong&gt;group averages reconstructed&lt;/strong&gt; from it. The fold changes and p-values are theirs.&lt;/p&gt;</t>
+          <t>Undifferentiated</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -3479,12 +2452,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>group A name</t>
+          <t>group A short name</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Undifferentiated</t>
+          <t>Undiff</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
@@ -3503,12 +2476,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>group A short name</t>
+          <t>group A description</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Undiff</t>
+          <t>CAD cells in serum, dividing. 3 dishes.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
@@ -3527,12 +2500,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>group A description</t>
+          <t>group B name</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>CAD cells in serum, dividing. 3 dishes.</t>
+          <t>Differentiated</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
@@ -3551,12 +2524,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>group B name</t>
+          <t>group B short name</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Differentiated</t>
+          <t>Diff</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
@@ -3575,12 +2548,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>group B short name</t>
+          <t>group B description</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>5 days serum-free (DMEM/F12 + ITS), neurite-like processes. 3 dishes.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
@@ -3599,12 +2572,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>group B description</t>
+          <t>primary short name (group B)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>5 days serum-free (DMEM/F12 + ITS), neurite-like processes. 3 dishes.</t>
+          <t>Differentiated</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
@@ -3623,12 +2596,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>primary short name (group B)</t>
+          <t>primary short name (group A)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Differentiated</t>
+          <t>Undifferentiated</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
@@ -3647,12 +2620,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>primary short name (group A)</t>
+          <t>primary name</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Undifferentiated</t>
+          <t>differentiated vs undifferentiated</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
@@ -3671,12 +2644,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>primary name</t>
+          <t>primary stats note</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>differentiated vs undifferentiated</t>
+          <t>(published result, Cevallos et al. 2025)</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
@@ -3695,12 +2668,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>primary stats note</t>
+          <t>units</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>(published result, Cevallos et al. 2025)</t>
+          <t>norm. counts</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -3719,12 +2692,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>theme 1 heading</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>norm. counts</t>
+          <t>ID inhibitors: the same master switch, now with statistics</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -3743,12 +2716,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>theme 1 heading</t>
+          <t>theme 2 heading</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>ID inhibitors: the same master switch, now with statistics</t>
+          <t>Neuronal genes switched ON</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -3767,12 +2740,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>theme 1 description</t>
+          <t>theme 3 heading</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>The identical result as the backup data, but with 3 dishes per condition and real p-values. Id3 falls ~290x (p ≈ 4e-32). This is what replication looks like.</t>
+          <t>Cell division: shutting down</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
@@ -3791,12 +2764,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>theme 2 heading</t>
+          <t>theme 4 heading</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Neuronal genes switched ON</t>
+          <t>Biggest increases</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
@@ -3815,12 +2788,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>theme 2 description</t>
+          <t>theme 5 heading</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>With more statistical power, the published study detects the neuronal program the single-dish experiment could only hint at: ion channels, synapse proteins and axon-growth genes all rise.</t>
+          <t>Biggest decreases</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
@@ -3839,12 +2812,12 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>theme 3 heading</t>
+          <t>theme 6 heading</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Cell division: shutting down</t>
+          <t>Housekeeping genes: a built-in health check</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
@@ -3863,12 +2836,12 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>theme 3 description</t>
+          <t>summary "up" stat caption</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Differentiating neurons exit the cell cycle. Every one of these falls significantly.</t>
+          <t>genes significantly UP when differentiated</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
@@ -3887,60 +2860,43 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>theme 4 heading</t>
+          <t>summary "down" stat caption</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Biggest increases</t>
+          <t>genes significantly DOWN when differentiated</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>D023</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Tab 1: Published study</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>theme 4 description</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>The strongest inductions in the published data: extracellular-matrix and membrane genes as the cells build neurites.</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Tab 3: Backup data</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>D024</t>
+          <t>D023</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Tab 1: Published study</t>
+          <t>Tab 3: Backup data</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>theme 5 heading</t>
+          <t>tab label</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Biggest decreases</t>
+          <t>③ Backup data (1 dish each)</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -3949,22 +2905,22 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D024</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Tab 1: Published study</t>
+          <t>Tab 3: Backup data</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>theme 5 description</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>The strongest losses. Note Id3 and Id2 near the top, plus Dbh and Sctr, the same genes the backup data flagged.</t>
+          <t>Backup data: what happens when a cell becomes a neuron?</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
@@ -3973,22 +2929,22 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>D026</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Tab 1: Published study</t>
+          <t>Tab 3: Backup data</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>theme 6 heading</t>
+          <t>sub-heading</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Housekeeping genes: a built-in health check</t>
+          <t>Backup data · mouse CAD cells · undifferentiated vs differentiated · 1 dish each · descriptive comparison (no statistics)</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
@@ -3997,22 +2953,22 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>D027</t>
+          <t>D026</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Tab 1: Published study</t>
+          <t>Tab 3: Backup data</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>theme 6 description</t>
+          <t>group A name</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Genes every cell needs constantly. They shift only slightly (well under 2x) even though the p-values are tiny, a reminder that with enough replicates, statistically significant does not mean biologically large.</t>
+          <t>Undifferentiated</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
@@ -4021,22 +2977,22 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>D028</t>
+          <t>D027</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Tab 1: Published study</t>
+          <t>Tab 3: Backup data</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>summary "up" stat caption</t>
+          <t>group A short name</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>genes significantly UP when differentiated</t>
+          <t>Undiff</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr"/>
@@ -4045,33 +3001,50 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>D029</t>
+          <t>D028</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Tab 1: Published study</t>
+          <t>Tab 3: Backup data</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>summary "down" stat caption</t>
+          <t>group A description</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>genes significantly DOWN when differentiated</t>
+          <t>CAD cells growing in serum, dividing and immature.</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Tab 3: Backup data</t>
         </is>
       </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>group B name</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Differentiated</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -4086,12 +3059,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>tab label</t>
+          <t>group B short name</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>③ Backup data (1 dish each)</t>
+          <t>Diff</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr"/>
@@ -4110,12 +3083,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>group B description</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Backup data: what happens when a cell becomes a neuron?</t>
+          <t>Serum removed for 5 days, so cells stop dividing and mature.</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr"/>
@@ -4134,12 +3107,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>sub-heading</t>
+          <t>primary short name (group B)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Backup data · mouse CAD cells · undifferentiated vs differentiated · 1 dish each · descriptive comparison (no statistics)</t>
+          <t>Differentiated</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr"/>
@@ -4158,20 +3131,16 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>intro paragraph</t>
+          <t>primary short name (group A)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong style="color:var(--text)"&gt;CAD cells&lt;/strong&gt; are a mouse line derived from catecholaminergic neurons. In serum they divide in an immature state. Remove the serum and they &lt;span class="term" title="Stop dividing and mature into a specialised cell type."&gt;differentiate&lt;/span&gt;: they stop dividing and grow long neuron-like processes.&lt;/p&gt;&lt;p&gt;Here one dish of each was sequenced. Your job: work out which genes drive that switch. Start with &lt;strong style="color:var(--gold)"&gt;Id2&lt;/strong&gt; or &lt;strong style="color:var(--gold)"&gt;Id3&lt;/strong&gt;. They tell the clearest story.&lt;/p&gt;&lt;p class="hint"&gt;⚠ One dish per condition means &lt;strong&gt;no p-values are possible&lt;/strong&gt;. Everything here is descriptive. When you find something interesting, check it against the published study, which ran the same experiment &lt;em&gt;with&lt;/em&gt; replicates.&lt;/p&gt;</t>
+          <t>Undifferentiated</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -4186,12 +3155,12 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>group A name</t>
+          <t>primary name</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Undifferentiated</t>
+          <t>differentiated vs undifferentiated</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr"/>
@@ -4210,12 +3179,12 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>group A short name</t>
+          <t>units</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Undiff</t>
+          <t>CPM</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr"/>
@@ -4234,12 +3203,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>group A description</t>
+          <t>theme 1 heading</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>CAD cells growing in serum, dividing and immature.</t>
+          <t>ID inhibitors &amp; TGF-β: the master switch</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr"/>
@@ -4258,12 +3227,12 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>group B name</t>
+          <t>theme 2 heading</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Differentiated</t>
+          <t>Neuron identity markers: already on</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr"/>
@@ -4282,12 +3251,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>group B short name</t>
+          <t>theme 3 heading</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>Cell division: easing off</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr"/>
@@ -4306,12 +3275,12 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>group B description</t>
+          <t>theme 4 heading</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Serum removed for 5 days, so cells stop dividing and mature.</t>
+          <t>Stress &amp; cholesterol: switched on</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr"/>
@@ -4330,12 +3299,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>primary short name (group B)</t>
+          <t>theme 5 heading</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Differentiated</t>
+          <t>Housekeeping genes: a built-in health check</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr"/>
@@ -4354,12 +3323,12 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>primary short name (group A)</t>
+          <t>summary "up" stat caption</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Undifferentiated</t>
+          <t>genes &gt;2x higher when differentiated</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr"/>
@@ -4378,334 +3347,22 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>primary name</t>
+          <t>summary "down" stat caption</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>differentiated vs undifferentiated</t>
+          <t>genes &gt;2x lower when differentiated</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>D043</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>CPM</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr"/>
-      <c r="F48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>D044</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>theme 1 heading</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>ID inhibitors &amp; TGF-β: the master switch</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr"/>
-      <c r="F49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>D045</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>theme 1 description</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>ID proteins actively BLOCK differentiation. Watch them collapse: losing Id1/Id2/Id3 is the molecular event that lets the cell mature. The published study sees exactly the same thing.</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr"/>
-      <c r="F50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>D046</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>theme 2 heading</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Neuron identity markers: already on</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr"/>
-      <c r="F51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>D047</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>theme 2 description</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>The surprise: these barely change. CAD cells are ALREADY neuron-like before differentiation, so the switch is not "become a neuron from scratch". It is "stop dividing and mature". Pcp4 and Gng4 are the ones that do rise.</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr"/>
-      <c r="F52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>D048</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>theme 3 heading</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>Cell division: easing off</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr"/>
-      <c r="F53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>D049</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>theme 3 description</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Differentiated neurons stop dividing, and these genes do fall, but gently. Compare the magnitudes with the published study, which had replicates and could prove it.</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr"/>
-      <c r="F54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>theme 4 heading</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Stress &amp; cholesterol: switched on</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>D051</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>theme 4 description</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Differentiation is metabolically demanding. Cholesterol-synthesis genes (neurons need lots of membrane) and stress-response genes rise.</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr"/>
-      <c r="F56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>D052</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>theme 5 heading</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Housekeeping genes: a built-in health check</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr"/>
-      <c r="F57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>D053</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>theme 5 description</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Genes every cell needs constantly. Here they are beautifully flat (all within ~1.3x), exactly what healthy, deliberate differentiation looks like, and a sign the two samples are technically comparable.</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>summary "up" stat caption</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>genes &gt;2x higher when differentiated</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>D055</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Tab 3: Backup data</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>summary "down" stat caption</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>genes &gt;2x lower when differentiated</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4717,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4940,15 +3597,11 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong style="color:var(--text)"&gt;Cevallos et al. 2025&lt;/strong&gt;, an independent published experiment on the same cells.</t>
+          <t>Too few matching genes to compare.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4968,11 +3621,15 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Agreement between two separate labs is the strongest evidence a finding is real.</t>
+          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -4992,7 +3649,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>With one dish per condition there are no p-values here, so agreement with an independent lab is the only real evidence available.</t>
+          <t>Strong agreement with the published study.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
@@ -5016,15 +3673,11 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>If the two experiments agree, dots line up along the &lt;span style="color:var(--gold)"&gt;gold diagonal&lt;/span&gt;.</t>
+          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -5044,7 +3697,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Dots in the top-right and bottom-left quadrants agree in direction; the other two quadrants disagree.</t>
+          <t>Little agreement with this particular study.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
@@ -5068,15 +3721,11 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong style="color:var(--gold)"&gt;Click a dot&lt;/strong&gt; to open that gene.</t>
+          <t>The file needs a header row and at least one gene row.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -5096,15 +3745,11 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
+          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -5124,7 +3769,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Different experiments, cells and sequencing runs, so agreement here is meaningful, and disagreement on weakly-expressed genes is normal.</t>
+          <t>Assign at least one sample to a group.</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -5148,7 +3793,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Strong agreement with the published study.</t>
+          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -5172,7 +3817,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
+          <t>The 25 most-decreased well-expressed genes.</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -5196,155 +3841,11 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Little agreement with this particular study.</t>
+          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>A018</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>The file needs a header row and at least one gene row.</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>A019</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Could not find at least two numeric sample columns. Check that the first row is a header and the other columns are numbers.</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>A020</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Assign at least one sample to each group.</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>A021</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>A022</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>The 25 most-decreased well-expressed genes.</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr"/>
-      <c r="F26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>A023</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/editing/CAD_Explorer_text.xlsx
+++ b/editing/CAD_Explorer_text.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Run analysis →</t>
+          <t>one condition only: compare against the published study. Mine are</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr"/>
@@ -2029,43 +2029,60 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>&lt;button&gt;</t>
+          <t>&lt;option&gt; value</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>⬇ Export results (CSV)</t>
+          <t>dif</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Cross-check vs published</t>
-        </is>
-      </c>
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>H051</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Your own data (upload)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>&lt;option&gt;</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>differentiated</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>H051</t>
+          <t>H052</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Cross-check vs published</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>&lt;h2&gt;</t>
+          <t>&lt;option&gt; value</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Does your result match the published study?</t>
+          <t>undiff</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr"/>
@@ -2074,22 +2091,22 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>H052</t>
+          <t>H053</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Cross-check vs published</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;option&gt;</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Gene-by-gene agreement</t>
+          <t>undifferentiated</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
@@ -2098,22 +2115,22 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>H053</t>
+          <t>H054</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Cross-check vs published</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>&lt;h3&gt;</t>
+          <t>&lt;button&gt;</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Landmark genes: the ones this experiment is known for</t>
+          <t>Run analysis →</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
@@ -2122,50 +2139,33 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>H054</t>
+          <t>H055</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Cross-check vs published</t>
+          <t>Your own data (upload)</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>&lt;th&gt;</t>
+          <t>&lt;button&gt;</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Gene</t>
+          <t>⬇ Export results (CSV)</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>H055</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Cross-check vs published</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>&lt;th&gt;</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>What it is</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>&lt;th&gt;</t>
+          <t>&lt;h2&gt;</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Your log₂FC</t>
+          <t>Does your result match the published study?</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>&lt;th&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Published log₂FC</t>
+          <t>Gene-by-gene agreement</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>&lt;th&gt;</t>
+          <t>&lt;h3&gt;</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Agree?</t>
+          <t>Landmark genes: the ones this experiment is known for</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
@@ -2252,25 +2252,145 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>&lt;footer&gt;</t>
+          <t>&lt;th&gt;</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>CAD Gene Explorer · mouse RNA-seq · built for teaching · your uploaded files never leave your computer</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>H060</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>&lt;th&gt;</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>H061</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>&lt;th&gt;</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Your log₂FC</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>H062</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>&lt;th&gt;</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Published log₂FC</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>H063</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>&lt;th&gt;</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Agree?</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>H064</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>Cross-check vs published</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>&lt;footer&gt;</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>CAD Gene Explorer · mouse RNA-seq · built for teaching · your uploaded files never leave your computer</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A15:F15"/>
@@ -3374,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3525,7 +3645,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Click a row to open that gene.</t>
+          <t>Dots are your individual dishes. The published bar is a reconstructed group mean, so it has no dots.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
@@ -3549,7 +3669,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Does your result match the published study?</t>
+          <t>Click a row to open that gene.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
@@ -3573,7 +3693,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Does the backup data match the published study?</t>
+          <t>Does your result match the published study?</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
@@ -3597,7 +3717,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Too few matching genes to compare.</t>
+          <t>Does the backup data match the published study?</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
@@ -3621,15 +3741,11 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
+          <t>Too few matching genes to compare.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3649,11 +3765,15 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Strong agreement with the published study.</t>
+          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3673,7 +3793,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
+          <t>Strong agreement with the published study.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
@@ -3697,7 +3817,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Little agreement with this particular study.</t>
+          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
@@ -3721,7 +3841,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>The file needs a header row and at least one gene row.</t>
+          <t>Little agreement with this particular study.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
@@ -3745,7 +3865,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
+          <t>The file needs a header row and at least one gene row.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
@@ -3769,7 +3889,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Assign at least one sample to a group.</t>
+          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -3793,7 +3913,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
+          <t>Assign at least one sample to a group.</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -3817,7 +3937,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>The 25 most-decreased well-expressed genes.</t>
+          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -3841,11 +3961,159 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
+          <t>The published dataset is not loaded, so there is nothing to borrow from.</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>A018</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Could not read the published condition needed for this comparison.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>A019</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Cross-study comparison.&lt;/strong&gt; Only one of your conditions was uploaded, so the other half comes from Cevallos et al.</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>A020</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Different lab, different library prep and different normalisation, so part of any difference is technical rather than biological.</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>A021</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Large, consistent changes are still meaningful; small ones are not. There are no p-values, and the published cross-check is switched off because this comparison already uses that data.</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>A022</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>The 25 most-decreased well-expressed genes.</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>A023</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/editing/CAD_Explorer_text.xlsx
+++ b/editing/CAD_Explorer_text.xlsx
@@ -3494,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Does your result match the published study?</t>
+          <t>The published dataset is not available.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Does the backup data match the published study?</t>
+          <t>A fold-change correlation is not shown: it would share a denominator with the borrowed half and agree with itself.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Too few matching genes to compare.</t>
+          <t>Expression levels in your samples against the matching published condition. Both sides are counts per million.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
@@ -3765,15 +3765,11 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
+          <t>Your sample looks like the published one.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3793,7 +3789,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Strong agreement with the published study.</t>
+          <t>Broadly similar, with real differences.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
@@ -3817,7 +3813,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
+          <t>Expect some of that from a different lab and library prep; large systematic gaps are worth a look.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
@@ -3841,7 +3837,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Little agreement with this particular study.</t>
+          <t>The profiles do not match closely.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
@@ -3865,7 +3861,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>The file needs a header row and at least one gene row.</t>
+          <t>That can mean a different cell state, a technical problem with the run, or gene names that did not line up.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
@@ -3889,7 +3885,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
+          <t>Does your result match the published study?</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -3913,7 +3909,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Assign at least one sample to a group.</t>
+          <t>Does the backup data match the published study?</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -3937,7 +3933,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
+          <t>Too few matching genes to compare.</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -3961,11 +3957,15 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>The published dataset is not loaded, so there is nothing to borrow from.</t>
+          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Could not read the published condition needed for this comparison.</t>
+          <t>Strong agreement with the published study.</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
@@ -4009,15 +4009,11 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Cross-study comparison.&lt;/strong&gt; Only one of your conditions was uploaded, so the other half comes from Cevallos et al.</t>
+          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -4037,7 +4033,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Different lab, different library prep and different normalisation, so part of any difference is technical rather than biological.</t>
+          <t>Little agreement with this particular study.</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
@@ -4061,7 +4057,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Large, consistent changes are still meaningful; small ones are not. There are no p-values, and the published cross-check is switched off because this comparison already uses that data.</t>
+          <t>The file needs a header row and at least one gene row.</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
@@ -4085,7 +4081,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>The 25 most-decreased well-expressed genes.</t>
+          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr"/>
@@ -4109,11 +4105,207 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
+          <t>Assign at least one sample to a group.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>A024</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>A025</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>The published dataset is not loaded, so there is nothing to borrow from.</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>A026</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Could not read the published condition needed for this comparison.</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>A027</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Cross-study comparison.&lt;/strong&gt; Only one of your conditions was uploaded, so the other half comes from Cevallos et al.</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>A028</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Different lab, different library prep and different normalisation, so part of any difference is technical rather than biological.</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>A029</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Large, consistent changes are still meaningful; small ones are not. There are no p-values, and the published cross-check is switched off because this comparison already uses that data.</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>A030</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>The 25 most-decreased well-expressed genes.</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>A031</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Messages shown while using the page</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/editing/CAD_Explorer_text.xlsx
+++ b/editing/CAD_Explorer_text.xlsx
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Results read as &lt;strong style="color:var(--text)"&gt;B relative to A&lt;/strong&gt;. One group on its own is fine: you get expression levels, no comparison.</t>
+          <t>Results read as &lt;strong style="color:var(--text)"&gt;B relative to A&lt;/strong&gt;. One group on its own gives expression levels only.</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>CAD Gene Explorer · mouse RNA-seq · built for teaching · your uploaded files never leave your computer</t>
+          <t>CAD Gene Explorer · your files never leave your computer</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Mouse CAD cells · undifferentiated vs differentiated · 3 dishes each · DESeq2 results from GEO GSE291553</t>
+          <t>Mouse CAD cells · 3 dishes each · DESeq2 from GEO GSE291553</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Backup data · mouse CAD cells · undifferentiated vs differentiated · 1 dish each · descriptive comparison (no statistics)</t>
+          <t>Backup data · mouse CAD cells · 1 dish each · no statistics</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
@@ -3494,7 +3494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Search for a gene above, click a chip, or pick a random one to get started.</t>
+          <t>This gene had too few reads to be tested statistically.</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr"/>
@@ -3593,11 +3593,15 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>This gene had too few reads to be tested statistically.</t>
+          <t>Bars are &lt;strong&gt;reconstructed group means&lt;/strong&gt;. Individual dish values were never published, so there are no dots.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3617,15 +3621,11 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Bars are &lt;strong&gt;group averages reconstructed&lt;/strong&gt; from the published summary table. The individual dish values were not deposited, so no dots are shown.</t>
+          <t>Dots are your dishes. The published bar is a reconstructed mean, so it has none.</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Dots are your individual dishes. The published bar is a reconstructed group mean, so it has no dots.</t>
+          <t>Click a row to open that gene.</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Click a row to open that gene.</t>
+          <t>The published dataset is not available.</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr"/>
@@ -3693,11 +3693,15 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>The published dataset is not available.</t>
+          <t>&lt;strong&gt;⚠ Simulated practice file.&lt;/strong&gt; It was built from the published numbers, so it matches by construction.</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -3717,7 +3721,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>A fold-change correlation is not shown: it would share a denominator with the borrowed half and agree with itself.</t>
+          <t>Expression levels against the matching published condition, both as counts per million.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr"/>
@@ -3741,7 +3745,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Expression levels in your samples against the matching published condition. Both sides are counts per million.</t>
+          <t>Your sample looks like the published one.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr"/>
@@ -3765,7 +3769,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Your sample looks like the published one.</t>
+          <t>Broadly similar, with real differences.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr"/>
@@ -3789,7 +3793,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Broadly similar, with real differences.</t>
+          <t>Some of that is expected from a different lab. Large systematic gaps are worth a look.</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr"/>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Expect some of that from a different lab and library prep; large systematic gaps are worth a look.</t>
+          <t>The profiles do not match closely.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr"/>
@@ -3837,7 +3841,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>The profiles do not match closely.</t>
+          <t>That can mean a different cell state, a problem with the run, or gene names that did not line up.</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr"/>
@@ -3861,7 +3865,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>That can mean a different cell state, a technical problem with the run, or gene names that did not line up.</t>
+          <t>Does your result match the published study?</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
@@ -3885,7 +3889,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Does your result match the published study?</t>
+          <t>Does the backup data match the published study?</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr"/>
@@ -3909,7 +3913,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Does the backup data match the published study?</t>
+          <t>Too few matching genes to compare.</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
@@ -3933,7 +3937,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Too few matching genes to compare.</t>
+          <t>Strong agreement with the published study.</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -3957,15 +3961,11 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;⚠ This file is the simulated practice dataset.&lt;/strong&gt; It was generated &lt;em&gt;from&lt;/em&gt; the published study\'s own numbers, so it will match almost perfectly by construction. That is circular: it shows the comparison working, not a real replication. Upload genuine data to get a meaningful answer.</t>
+          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Strong agreement with the published study.</t>
+          <t>Little agreement with this particular study.</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Moderate agreement: the broad story matches, the details are noisy.</t>
+          <t>The file needs a header row and at least one gene row.</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Little agreement with this particular study.</t>
+          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>The file needs a header row and at least one gene row.</t>
+          <t>Assign at least one sample to a group.</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Could not find a numeric sample column. Check that the first row is a header and the other columns are numbers.</t>
+          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Assign at least one sample to a group.</t>
+          <t>The published dataset is not loaded, so there is nothing to borrow from.</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Fewer than 50 expressed genes found. Is the first column the gene name and the others numeric?</t>
+          <t>Could not read the published condition needed for this comparison.</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr"/>
@@ -4153,11 +4153,15 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>The published dataset is not loaded, so there is nothing to borrow from.</t>
+          <t>&lt;strong&gt;Cross-study comparison.&lt;/strong&gt; Only one of your conditions was uploaded, so the other half comes from Cevallos et al.</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="7" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -4177,7 +4181,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Could not read the published condition needed for this comparison.</t>
+          <t>The 25 most-decreased well-expressed genes.</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr"/>
@@ -4201,111 +4205,11 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Cross-study comparison.&lt;/strong&gt; Only one of your conditions was uploaded, so the other half comes from Cevallos et al.</t>
+          <t>Genes every cell needs all the time. Big moves usually mean something technical.</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>A028</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Different lab, different library prep and different normalisation, so part of any difference is technical rather than biological.</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>A029</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Large, consistent changes are still meaningful; small ones are not. There are no p-values, and the published cross-check is switched off because this comparison already uses that data.</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>A030</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>The 25 most-decreased well-expressed genes.</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>A031</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Messages shown while using the page</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Genes every cell needs all the time. If these move a lot, either the cells are in serious trouble or something technical went wrong.</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
